--- a/artfynd/A 29144-2023 artfynd.xlsx
+++ b/artfynd/A 29144-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 29144-2023 artfynd.xlsx
+++ b/artfynd/A 29144-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY13"/>
+  <dimension ref="A1:AY15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>93434072</v>
+        <v>60246954</v>
       </c>
       <c r="B2" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,50 +686,44 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>250m V om väg, Dlr</t>
+          <t>Snöklinten, västsluttning Klintklacken, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>502423.6427406843</v>
+        <v>502258</v>
       </c>
       <c r="R2" t="n">
-        <v>6669315.872118049</v>
+        <v>6669211</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -761,22 +750,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2021-05-12</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2016-06-22</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2021-05-12</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2016-06-22</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -785,19 +764,53 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>Blåbärsbarrskog</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>120-150 årig ogallrad skog frisk - fuktig</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>gammal gran</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies # gammal gran</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Anders Erixon</t>
+          <t>Janolof Hermansson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Anders Erixon</t>
+          <t>Janolof Hermansson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -807,12 +820,7 @@
         <v>93433857</v>
       </c>
       <c r="B3" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -856,10 +864,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>502492.9247327506</v>
+        <v>502493</v>
       </c>
       <c r="R3" t="n">
-        <v>6669355.742039354</v>
+        <v>6669356</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -889,19 +897,9 @@
           <t>2021-05-12</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2021-05-12</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -934,15 +932,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>93434188</v>
+        <v>93433885</v>
       </c>
       <c r="B4" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,12 +962,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -986,14 +979,14 @@
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>200m V om vägen, Dlr</t>
+          <t>45m V om väg, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>502421.6429743475</v>
+        <v>502472</v>
       </c>
       <c r="R4" t="n">
-        <v>6669323.835524639</v>
+        <v>6669367</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1023,19 +1016,9 @@
           <t>2021-05-12</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2021-05-12</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1063,15 +1046,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>93434264</v>
+        <v>93433931</v>
       </c>
       <c r="B5" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1098,7 +1076,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>170</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1115,14 +1093,14 @@
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Runt tallen, Dlr</t>
+          <t>100m V om väg, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>502438.5929243267</v>
+        <v>502471</v>
       </c>
       <c r="R5" t="n">
-        <v>6669328.82470555</v>
+        <v>6669337</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1152,19 +1130,9 @@
           <t>2021-05-12</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2021-05-12</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1192,15 +1160,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>93434155</v>
+        <v>93433949</v>
       </c>
       <c r="B6" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1227,7 +1190,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1244,14 +1207,14 @@
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>250m V om vägen, Dlr</t>
+          <t>110m V om väg, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>502409.6798926421</v>
+        <v>502464</v>
       </c>
       <c r="R6" t="n">
-        <v>6669317.854098165</v>
+        <v>6669326</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1281,19 +1244,9 @@
           <t>2021-05-12</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2021-05-12</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1321,15 +1274,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>93434135</v>
+        <v>93433974</v>
       </c>
       <c r="B7" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1356,7 +1304,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1373,14 +1321,14 @@
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>300m V om väg, Dlr</t>
+          <t>130m V om väg, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>502395.2116045444</v>
+        <v>502453</v>
       </c>
       <c r="R7" t="n">
-        <v>6669330.289490686</v>
+        <v>6669332</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1410,19 +1358,9 @@
           <t>2021-05-12</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2021-05-12</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1450,15 +1388,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>93433974</v>
+        <v>93434019</v>
       </c>
       <c r="B8" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1485,7 +1418,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1502,14 +1435,14 @@
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>130m V om väg, Dlr</t>
+          <t>200m V om väg, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>502452.5520834137</v>
+        <v>502459</v>
       </c>
       <c r="R8" t="n">
-        <v>6669332.318575107</v>
+        <v>6669331</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1539,19 +1472,9 @@
           <t>2021-05-12</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2021-05-12</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1579,15 +1502,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>93434019</v>
+        <v>93434072</v>
       </c>
       <c r="B9" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1614,7 +1532,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1631,14 +1549,14 @@
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>200m V om väg, Dlr</t>
+          <t>250m V om väg, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>502458.536241053</v>
+        <v>502424</v>
       </c>
       <c r="R9" t="n">
-        <v>6669331.326995229</v>
+        <v>6669316</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1668,19 +1586,9 @@
           <t>2021-05-12</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2021-05-12</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1708,15 +1616,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>93433931</v>
+        <v>93434135</v>
       </c>
       <c r="B10" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1743,7 +1646,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>170</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1760,14 +1663,14 @@
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>100m V om väg, Dlr</t>
+          <t>300m V om väg, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>502471.4964461949</v>
+        <v>502395</v>
       </c>
       <c r="R10" t="n">
-        <v>6669337.30923143</v>
+        <v>6669330</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1797,19 +1700,9 @@
           <t>2021-05-12</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2021-05-12</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1837,15 +1730,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>93433949</v>
+        <v>93434155</v>
       </c>
       <c r="B11" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1872,7 +1760,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>90</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1889,14 +1777,14 @@
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>110m V om väg, Dlr</t>
+          <t>250m V om vägen, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>502463.5258289065</v>
+        <v>502410</v>
       </c>
       <c r="R11" t="n">
-        <v>6669326.352401562</v>
+        <v>6669318</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1926,19 +1814,9 @@
           <t>2021-05-12</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2021-05-12</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1966,15 +1844,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>93433885</v>
+        <v>93434188</v>
       </c>
       <c r="B12" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2001,12 +1874,12 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>160</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -2018,14 +1891,14 @@
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>45m V om väg, Dlr</t>
+          <t>200m V om vägen, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>502471.9749318608</v>
+        <v>502422</v>
       </c>
       <c r="R12" t="n">
-        <v>6669367.177021598</v>
+        <v>6669324</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -2055,19 +1928,9 @@
           <t>2021-05-12</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2021-05-12</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2098,12 +1961,7 @@
         <v>93434216</v>
       </c>
       <c r="B13" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2151,10 +2009,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>502420.6529542094</v>
+        <v>502421</v>
       </c>
       <c r="R13" t="n">
-        <v>6669312.883365445</v>
+        <v>6669313</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2184,19 +2042,9 @@
           <t>2021-05-12</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2021-05-12</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2221,6 +2069,234 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>93434264</v>
+      </c>
+      <c r="B14" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Runt tallen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>502439</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6669329</v>
+      </c>
+      <c r="S14" t="n">
+        <v>5</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2021-05-12</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2021-05-12</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Anders Erixon</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Anders Erixon</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>86950665</v>
+      </c>
+      <c r="B15" t="n">
+        <v>102464</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>221343</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Brunklöver</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Trifolium spadiceum</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Längs båda sidor av vägen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>502547</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6669290</v>
+      </c>
+      <c r="S15" t="n">
+        <v>25</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2020-07-10</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2020-07-10</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF15" t="inlineStr"/>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Anders Erixon</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Anders Erixon</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
